--- a/downloads/excel/Форма_расчета_сил_и_средств_привлекаемых_для_выполнения_мероприятий_при_угрозе_возникновения_ЧС.xlsx
+++ b/downloads/excel/Форма_расчета_сил_и_средств_привлекаемых_для_выполнения_мероприятий_при_угрозе_возникновения_ЧС.xlsx
@@ -63,7 +63,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -85,20 +85,100 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -469,10 +549,10 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
@@ -486,7 +566,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -503,86 +582,84 @@
           <t>Описание</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>N п/п</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Наименование формирования</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Ведомственная принадлежность</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Срок готов-
 ности</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Место дислокации, телефоны ДДС</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Численность формирования (общая, дежурная смена)</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Оснащение основными видами техники</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Виды выполняемых работ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr"/>
-      <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr"/>
-      <c r="B6" s="3" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr"/>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>